--- a/prospection/Prospection_Logistique_Nord-Est_Reunion.xlsx
+++ b/prospection/Prospection_Logistique_Nord-Est_Reunion.xlsx
@@ -21,13 +21,13 @@
     <sheet name="11 Sources &amp; mise à jour" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 Saint-Denis'!$A$4:$U$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Sainte-Marie'!$A$4:$U$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03 Sainte-Suzanne'!$A$4:$U$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04 Saint-André'!$A$4:$U$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05 Bras-Panon'!$A$4:$U$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06 Saint-Benoît'!$A$4:$U$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07 Sainte-Rose &amp; Hauteurs'!$A$4:$U$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 Saint-Denis'!$A$4:$V$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Sainte-Marie'!$A$4:$V$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03 Sainte-Suzanne'!$A$4:$V$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04 Saint-André'!$A$4:$V$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05 Bras-Panon'!$A$4:$V$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06 Saint-Benoît'!$A$4:$V$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07 Sainte-Rose &amp; Hauteurs'!$A$4:$V$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C24"/>
+  <dimension ref="B2:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -776,6 +776,74 @@
       <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Trame d'appel à froid, argumentaire employeur et réponses aux objections les plus fréquentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>11 Sources &amp; mise à jour</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>D'où viennent les données, et où aller les actualiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>REMPLISSAGE AUTOMATIQUE – 2 MINUTES</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="39" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Le script d'auto-complétion</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Le fichier « completer_via_annuaire.py » (fourni à côté de ce classeur) interroge l'API officielle de l'INSEE (recherche-entreprises.api.gouv.fr) et remplit tout seul les colonnes SIRET, Code APE, Libellé APE, Effectif et Dirigeant, pour toutes les lignes du fichier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="39" customHeight="1">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Comment le lancer</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Sur Mac : ouvrir le Terminal. Sur PC : ouvrir l'invite de commandes. Taper : python3 completer_via_annuaire.py  (voir le fichier LISEZ-MOI.md pour le détail). Le script crée une COPIE enrichie et ne touche jamais à votre fichier de travail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Ce qu'il ne fait pas</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Il ne remplit ni les téléphones ni les emails : ces données ne sont dans aucune base ouverte. Il ne remplit une case QUE s'il est sûr de l'entreprise ; sinon il laisse « A VERIFIER » et note le doute dans le journal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>La colonne Effectif</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Tranche d'effectif salarié INSEE. C'est votre filtre le plus utile : une entreprise de 0 salarié ne pourra pas tutorer un apprenti, une entreprise de 10 à 50 salariés est la cible idéale.</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1717,49 +1785,137 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Annuaire fret – Aéroport Roland Garros</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>https://www.reunion.aeroport.fr/fret/annuaire</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Kompass – Transports et logistique Saint-André</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>https://fr.kompass.com/s/transports-et-logistique/10/v/saint-andre/fr_04_974_97409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Pages Jaunes – fiche SIRET Créole Logistique Transport</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>https://www.pagesjaunes.fr/siret/80216938300014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Tereos Océan Indien (sucrerie de Bois-Rouge)</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>https://www.tereos.re/visitez-nos-sucreries/sucrerie-de-bois-rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Groupe SIPR / CERP Réunion (répartition pharmaceutique)</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>https://www.cerp-sipr.com/cerp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>SIFA Logistics – agence Réunion</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>https://sifalogistics.com/nos-agences/sifa-reunion/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>LIMITES CONNUES</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>• Les SIRET, codes APE et noms de dirigeants non confirmés sont marqués « A VERIFIER » : ils ne sont PAS renseignés au hasard.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>• Les emails et téléphones directs ne figurent dans aucune base ouverte : ils se collectent sur le site de l'entreprise ou par téléphone.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>• Sainte-Rose, La Plaine-des-Palmistes et Salazie comptent très peu d'entreprises logistiques : le potentiel y est surtout en commerce de proximité et transport agricole.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>• Le fichier est une base de départ : il doit vivre. Ajoutez une ligne à chaque entreprise rencontrée sur le terrain.</t>
         </is>
       </c>
     </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>• Les entreprises ajoutées lors de l'enrichissement proviennent d'annuaires en ligne (annuaire fret de l'aéroport, Kompass, Pages Jaunes) : le NOM est fiable, l'adresse est à confirmer, et le SIRET reste à récupérer via le lien de la colonne S ou via le script d'auto-complétion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>• Une ligne porte la mention « A vérifier » en fiabilité (KUEHNE + NAGEL) : sa présence à La Réunion est citée mais non confirmée. Vérifiez-la sur l'Annuaire des Entreprises avant d'appeler.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A16:B16"/>
+  <mergeCells count="8">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
@@ -1770,6 +1926,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1781,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1793,18 +1955,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1869,60 +2032,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1979,15 +2147,15 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -1997,33 +2165,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>Gestion d'entrepôt, livraison, suivi des flux, expédition. Profil idéal : préparateur de commandes.</t>
         </is>
@@ -2080,15 +2253,15 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2098,33 +2271,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr">
         <is>
           <t>Transport international + stockage, préparation de commandes, expédition.</t>
         </is>
@@ -2181,15 +2359,15 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2199,33 +2377,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>Routier, aérien, maritime + stockage et distribution.</t>
         </is>
@@ -2282,51 +2465,56 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="N8" s="19" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
         <is>
           <t>https://www.runlogistic.re/</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R8" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S8" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T8" s="20" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="17" t="inlineStr">
         <is>
           <t>Site : runlogistic.re — organisateur de transport.</t>
         </is>
@@ -2383,15 +2571,15 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2401,33 +2589,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="T9" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T9" s="14" t="inlineStr"/>
-      <c r="U9" s="11" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>Transport particuliers et professionnels.</t>
         </is>
@@ -2484,15 +2677,15 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2502,33 +2695,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P10" s="15" t="inlineStr">
+      <c r="Q10" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q10" s="15" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R10" s="19" t="inlineStr">
+      <c r="S10" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S10" s="15" t="inlineStr">
+      <c r="T10" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="17" t="inlineStr">
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="17" t="inlineStr">
         <is>
           <t>SIRET relevé sur base publique — à reconfirmer sur l'Annuaire des Entreprises.</t>
         </is>
@@ -2585,15 +2783,15 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2603,33 +2801,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P11" s="9" t="inlineStr">
+      <c r="Q11" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="R11" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R11" s="13" t="inlineStr">
+      <c r="S11" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S11" s="9" t="inlineStr">
+      <c r="T11" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T11" s="14" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr">
+      <c r="U11" s="14" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr">
         <is>
           <t>Filiale groupe SOMATRANS — commissionnaire en douane.</t>
         </is>
@@ -2686,15 +2889,15 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2704,33 +2907,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P12" s="15" t="inlineStr">
+      <c r="Q12" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q12" s="15" t="inlineStr">
+      <c r="R12" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R12" s="19" t="inlineStr">
+      <c r="S12" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S12" s="15" t="inlineStr">
+      <c r="T12" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="17" t="inlineStr">
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="17" t="inlineStr">
         <is>
           <t>Groupe national, process RH structuré : viser le siège + le responsable d'agence.</t>
         </is>
@@ -2787,15 +2995,15 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2805,33 +3013,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P13" s="9" t="inlineStr">
+      <c r="Q13" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="R13" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R13" s="13" t="inlineStr">
+      <c r="S13" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S13" s="9" t="inlineStr">
+      <c r="T13" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T13" s="14" t="inlineStr"/>
-      <c r="U13" s="11" t="inlineStr">
+      <c r="U13" s="14" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
         <is>
           <t>Entrepôt de stockage, clientèle CHR : fort besoin de préparation de commandes.</t>
         </is>
@@ -2888,15 +3101,15 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -2906,33 +3119,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P14" s="17" t="inlineStr">
         <is>
           <t>Magasinier / Gestion des stocks</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="R14" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R14" s="19" t="inlineStr">
+      <c r="S14" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S14" s="15" t="inlineStr">
+      <c r="T14" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T14" s="20" t="inlineStr"/>
-      <c r="U14" s="17" t="inlineStr">
+      <c r="U14" s="20" t="inlineStr"/>
+      <c r="V14" s="17" t="inlineStr">
         <is>
           <t>Emballages et fournitures pour la restauration.</t>
         </is>
@@ -2989,15 +3207,15 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -3007,33 +3225,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="R15" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R15" s="13" t="inlineStr">
+      <c r="S15" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S15" s="9" t="inlineStr">
+      <c r="T15" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T15" s="14" t="inlineStr"/>
-      <c r="U15" s="11" t="inlineStr">
+      <c r="U15" s="14" t="inlineStr"/>
+      <c r="V15" s="11" t="inlineStr">
         <is>
           <t>Glaces artisanales, livraison sur toute l'île : logistique du froid.</t>
         </is>
@@ -3090,15 +3313,15 @@
       </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="inlineStr">
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -3108,33 +3331,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P16" s="17" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P16" s="15" t="inlineStr">
+      <c r="Q16" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q16" s="15" t="inlineStr">
+      <c r="R16" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R16" s="19" t="inlineStr">
+      <c r="S16" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S16" s="15" t="inlineStr">
+      <c r="T16" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T16" s="20" t="inlineStr"/>
-      <c r="U16" s="17" t="inlineStr">
+      <c r="U16" s="20" t="inlineStr"/>
+      <c r="V16" s="17" t="inlineStr">
         <is>
           <t>Distributeur multimarques, logistique intégrée.</t>
         </is>
@@ -3191,15 +3419,15 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -3209,70 +3437,504 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
         <is>
           <t>Magasinier / Gestion des stocks</t>
         </is>
       </c>
-      <c r="P17" s="9" t="inlineStr">
+      <c r="Q17" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr">
+      <c r="R17" s="9" t="inlineStr">
         <is>
           <t>A vérifier</t>
         </is>
       </c>
-      <c r="R17" s="13" t="inlineStr">
+      <c r="S17" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S17" s="9" t="inlineStr">
+      <c r="T17" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T17" s="14" t="inlineStr"/>
-      <c r="U17" s="11" t="inlineStr">
+      <c r="U17" s="14" t="inlineStr"/>
+      <c r="V17" s="11" t="inlineStr">
         <is>
           <t>Filiale du groupe Ravate (siège Saint-Denis). Gros volumes = magasiniers/caristes.</t>
         </is>
       </c>
     </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>CERP RÉUNION (GROUPE SIPR)</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Répartition pharmaceutique / Dépositaire</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>97400</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
+        <is>
+          <t>https://www.cerp-sipr.com/cerp/</t>
+        </is>
+      </c>
+      <c r="P18" s="17" t="inlineStr">
+        <is>
+          <t>Opérateur logistique / Prépa. commandes</t>
+        </is>
+      </c>
+      <c r="Q18" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R18" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S18" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U18" s="20" t="inlineStr"/>
+      <c r="V18" s="17" t="inlineStr">
+        <is>
+          <t>Importateur-grossiste-répartiteur en produits pharmaceutiques. Groupe SIPR (CERP-Réunion, MAD-SIPR, Plurimed, Dicophar), 3 sites : Saint-Denis, Sainte-Marie, Saint-Pierre. Préparation de commandes sous Bonnes Pratiques de Distribution : cadre très formateur, gros volumes quotidiens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>CGF NORD</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Grossiste fruits &amp; légumes / Bio</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>91 rue Foch – Zone Foucherolles, Sainte-Clotilde</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>97490</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Sainte-Clotilde (Saint-Denis)</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Opérateur logistique / Prépa. commandes</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S19" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U19" s="14" t="inlineStr"/>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>Distribution en gros de fruits, légumes et produits bio : préparation de commandes quotidienne et gestion du froid. Rotation forte = besoin récurrent de préparateurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>SOMADIS – SOCIÉTÉ MANES DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Commerce de gros / Entrepôt</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>76 boulevard du Chaudron</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>97490</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Sainte-Clotilde (Saint-Denis)</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P20" s="17" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R20" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S20" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U20" s="20" t="inlineStr"/>
+      <c r="V20" s="17" t="inlineStr">
+        <is>
+          <t>Commerce de gros sur la zone du Chaudron : réception, stock, expédition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>DEMECO CHEUNG DÉMÉNAGEMENTS</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Déménagement / Garde-meuble</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>97400</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q21" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S21" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T21" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U21" s="14" t="inlineStr"/>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>Déménagement local, national et international, garde-meuble et groupage maritime. Manutention, inventaire et gestion de stock : bon terrain pour un profil magasinier.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:U17"/>
+  <autoFilter ref="A4:V21"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3284,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3296,18 +3958,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3372,60 +4035,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3482,51 +4150,56 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>https://sifalogistics.com/nos-agences/sifa-reunion/</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>Entrepôt sur zone aéroportuaire. Ouv. lun-jeu 8h-16h30, ven 8h-16h.</t>
         </is>
@@ -3583,15 +4256,15 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -3601,33 +4274,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr">
         <is>
           <t>Agence air.</t>
         </is>
@@ -3684,15 +4362,15 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -3702,33 +4380,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>Sur la plateforme fret.</t>
         </is>
@@ -3785,15 +4468,15 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -3803,33 +4486,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R8" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S8" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T8" s="20" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="17" t="inlineStr">
         <is>
           <t>Multimodal — bon terrain pour un apprenti agent de transit.</t>
         </is>
@@ -3886,51 +4574,56 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>0262 48 34 34</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="T9" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T9" s="14" t="inlineStr"/>
-      <c r="U9" s="11" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>Tél. relevé en annuaire public, à reconfirmer. Horaires : 8h-12h30 / 13h30-17h30, sam 8h30-12h. Tri et quai = poste d'agent de quai en alternance.</t>
         </is>
@@ -3987,15 +4680,15 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4005,33 +4698,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P10" s="15" t="inlineStr">
+      <c r="Q10" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q10" s="15" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R10" s="19" t="inlineStr">
+      <c r="S10" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S10" s="15" t="inlineStr">
+      <c r="T10" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="17" t="inlineStr">
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="17" t="inlineStr">
         <is>
           <t>Groupe international : passer par le responsable d'agence ET le service RH DOM.</t>
         </is>
@@ -4043,12 +4741,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>TRANS EXPRESS RÉUNION</t>
+          <t>TRANS EXPRESS RÉUNION (TER)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Transport express / Messagerie</t>
+          <t>Affrètement / Organisation de transports</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -4088,15 +4786,15 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4106,33 +4804,42 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R11" s="13" t="inlineStr">
+      <c r="S11" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S11" s="9" t="inlineStr">
+      <c r="T11" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T11" s="14" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr"/>
+      <c r="U11" s="14" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>Affrètement et organisation de transports. Présent à Gillot pour le fret aérien et au port pour le fret maritime : deux univers dans la même entreprise.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="15" t="n">
@@ -4145,7 +4852,7 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Transport / Logistique</t>
+          <t>Messagerie express internationale</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -4185,15 +4892,15 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4203,33 +4910,42 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>Opérateur logistique / Prépa. commandes</t>
-        </is>
-      </c>
-      <c r="P12" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
       <c r="Q12" s="15" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R12" s="15" t="inlineStr">
+        <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R12" s="19" t="inlineStr">
+      <c r="S12" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S12" s="15" t="inlineStr">
+      <c r="T12" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="17" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="17" t="inlineStr">
+        <is>
+          <t>Cité comme représentant officiel FedEx et TNT à La Réunion : quai, tri, documents d'expédition. Confirmer l'agrément lors de l'appel.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="9" t="n">
@@ -4237,17 +4953,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>SD BEAUSÉJOUR (supermarché)</t>
+          <t>HOLDTRANS</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Grande distribution – réserve</t>
+          <t>Transit / Commission en douane</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>200 avenue Beau Pays</t>
+          <t>Nouvelle aérogare de fret – porte 238</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -4282,15 +4998,15 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4300,35 +5016,40 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>Employé logistique en magasin</t>
-        </is>
-      </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Agent de transit / Déclarant douane jr</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R13" s="13" t="inlineStr">
+      <c r="S13" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S13" s="9" t="inlineStr">
+      <c r="T13" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T13" s="14" t="inlineStr"/>
-      <c r="U13" s="11" t="inlineStr">
-        <is>
-          <t>Réception marchandises / réserve : poste d'employé logistique.</t>
+      <c r="U13" s="14" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>Déclarants en douane agréés, fret maritime et aérien. Sur la plateforme fret de Gillot.</t>
         </is>
       </c>
     </row>
@@ -4338,130 +5059,884 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
+          <t>BOLLORÉ LOGISTICS RÉUNION</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Transit international / Logistique contractuelle</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>7 rue André Lardy – La Mare</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t>Agent de transit / Déclarant douane jr</t>
+        </is>
+      </c>
+      <c r="Q14" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R14" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S14" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T14" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U14" s="20" t="inlineStr"/>
+      <c r="V14" s="17" t="inlineStr">
+        <is>
+          <t>Groupe international : l'alternance y est une pratique installée. Viser le responsable d'agence ET la RH régionale, et déposer l'offre sur leur portail recrutement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>SCHENKER FRANCE – agence Réunion</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Transit / Commission de transport</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Zone aérogare de fret – Gillot</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>Agent de transit / Déclarant douane jr</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U15" s="14" t="inlineStr"/>
+      <c r="V15" s="11" t="inlineStr">
+        <is>
+          <t>Groupe international présent sur la zone fret. Même méthode que Bolloré : agence + RH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>KUEHNE + NAGEL – présence 974</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Transit / Logistique internationale</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P16" s="17" t="inlineStr">
+        <is>
+          <t>Agent de transit / Déclarant douane jr</t>
+        </is>
+      </c>
+      <c r="Q16" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R16" s="15" t="inlineStr">
+        <is>
+          <t>A vérifier</t>
+        </is>
+      </c>
+      <c r="S16" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T16" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U16" s="20" t="inlineStr"/>
+      <c r="V16" s="17" t="inlineStr">
+        <is>
+          <t>Présence citée sur la zone aéroportuaire mais NON confirmée : vérifier l'existence d'un établissement 974 sur l'Annuaire des Entreprises AVANT tout appel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>LEROY MERLIN SAINTE-MARIE</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Distribution spécialisée – réserve &amp; cour</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q17" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T17" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U17" s="14" t="inlineStr"/>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>Réception, réserve, cour matériaux, drive. Enseigne nationale : dossier alternance cadré. Passer par le magasin ET le portail recrutement de l'enseigne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>LA POSTE – centre courrier / colis Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Poste et courrier / Colis</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>2 rue Ravine</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O18" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P18" s="17" t="inlineStr">
+        <is>
+          <t>Agent de quai / Réception-expédition</t>
+        </is>
+      </c>
+      <c r="Q18" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R18" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S18" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U18" s="20" t="inlineStr"/>
+      <c r="V18" s="17" t="inlineStr">
+        <is>
+          <t>Tri et distribution de colis (Colissimo). Gros recruteur en alternance, mais dossier centralisé : passer par la RH régionale La Poste Réunion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>SIPR / MAD-SIPR – site Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Logistique pharmaceutique / Matériel médical</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S19" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U19" s="14" t="inlineStr"/>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>Groupe SIPR, 3 sites sur l'île. Magasin de matériel médical : gestion de stock et préparation de commandes tracées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>SD BEAUSÉJOUR (supermarché)</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Grande distribution – réserve</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>200 avenue Beau Pays</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>97438</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Sainte-Marie</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O20" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P20" s="17" t="inlineStr">
+        <is>
+          <t>Employé logistique en magasin</t>
+        </is>
+      </c>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R20" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S20" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U20" s="20" t="inlineStr"/>
+      <c r="V20" s="17" t="inlineStr">
+        <is>
+          <t>Réception marchandises / réserve : poste d'employé logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
           <t>U EXPRESS SAINTE-MARIE</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Grande distribution – réserve</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>112 rue Roger Payet</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>97438</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Sainte-Marie</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>A VERIFIER</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="N14" s="15" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="Q21" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="R21" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R14" s="19" t="inlineStr">
+      <c r="S21" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S14" s="15" t="inlineStr">
+      <c r="T21" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T14" s="20" t="inlineStr"/>
-      <c r="U14" s="17" t="inlineStr">
+      <c r="U21" s="14" t="inlineStr"/>
+      <c r="V21" s="11" t="inlineStr">
         <is>
           <t>Enseigne U : accords alternance fréquents.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U14"/>
+  <autoFilter ref="A4:V21"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4473,7 +5948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4485,18 +5960,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4561,60 +6037,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4671,15 +6152,15 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4689,33 +6170,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr"/>
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="15" t="n">
@@ -4768,15 +6254,15 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4786,33 +6272,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="9" t="n">
@@ -4865,15 +6356,15 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4883,33 +6374,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>TPE : vérifier la capacité à accueillir un apprenti (tuteur disponible).</t>
         </is>
@@ -4966,15 +6462,15 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -4984,56 +6480,61 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R8" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S8" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T8" s="20" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U8"/>
+  <autoFilter ref="A4:V8"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5045,7 +6546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5057,18 +6558,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5133,60 +6635,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5243,15 +6750,15 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5261,33 +6768,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Vérifié</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>SIRET du siège social relevé sur l'Annuaire des Entreprises. Entreprise récente : argument « construire votre équipe avec l'alternance ».</t>
         </is>
@@ -5344,15 +6856,15 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5362,33 +6874,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="9" t="n">
@@ -5441,15 +6958,15 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5459,33 +6976,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>Livraisons sur toute La Réunion.</t>
         </is>
@@ -5542,15 +7064,15 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5560,33 +7082,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Magasinier / Gestion des stocks</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R8" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S8" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T8" s="20" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="17" t="inlineStr">
         <is>
           <t>Vérifier l'activité exacte (code APE) avant l'appel.</t>
         </is>
@@ -5643,15 +7170,15 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5661,33 +7188,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Magasinier / Gestion des stocks</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="T9" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T9" s="14" t="inlineStr"/>
-      <c r="U9" s="11" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>Groupe structuré : passer par la RH régionale. Logistique de granulats et béton.</t>
         </is>
@@ -5744,15 +7276,15 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5762,33 +7294,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P10" s="15" t="inlineStr">
+      <c r="Q10" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q10" s="15" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R10" s="19" t="inlineStr">
+      <c r="S10" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S10" s="15" t="inlineStr">
+      <c r="T10" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="17" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="9" t="n">
@@ -5841,15 +7378,15 @@
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -5859,63 +7396,283 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P11" s="9" t="inlineStr">
+      <c r="Q11" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="R11" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R11" s="13" t="inlineStr">
+      <c r="S11" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S11" s="9" t="inlineStr">
+      <c r="T11" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T11" s="14" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr">
+      <c r="U11" s="14" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr">
         <is>
           <t>Réception / réserve / drive : plusieurs postes possibles.</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>TEREOS OCÉAN INDIEN – SUCRERIE DE BOIS-ROUGE</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Industrie sucrière / Flux &amp; expéditions</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>Bois-Rouge – Cambuston</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>97440</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Saint-André</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>https://www.tereos.re/</t>
+        </is>
+      </c>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q12" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="R12" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S12" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T12" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="17" t="inlineStr">
+        <is>
+          <t>Le plus gros site industriel de l'Est. Campagne sucrière de juillet à décembre : pics de flux, magasin de pièces, réception canne, expédition du sucre. Passer par la RH de Tereos Océan Indien (siège 974).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>SKAL BRICO SODIS</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Négoce de matériaux / Dépôt</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>705 chemin Lagourgue</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>97440</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Saint-André</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S13" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U13" s="14" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>Dépôt de matériaux : réception, cour, magasinier-cariste.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:U11"/>
+  <autoFilter ref="A4:V13"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5927,7 +7684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5939,18 +7696,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6015,60 +7773,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6090,7 +7853,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>A VERIFIER</t>
+          <t>22 bis RN2 – Rivière des Roches</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -6125,15 +7888,15 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -6143,35 +7906,40 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Vérifié</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>SIRET relevé sur base publique (siège Bras-Panon), à reconfirmer. Classée INSEE en transport de fret interurbain.</t>
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr">
+        <is>
+          <t>SIRET et adresse relevés sur base publique (siège Bras-Panon), à reconfirmer sur l'Annuaire des Entreprises. Classée INSEE en transport routier de fret interurbain. Entreprise installée depuis une dizaine d'années : tuteur potentiel expérimenté.</t>
         </is>
       </c>
     </row>
@@ -6226,15 +7994,15 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -6244,54 +8012,166 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>WIN LOCATION</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Location (activité à qualifier)</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>6 rue des Palmiers</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>97412</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Bras-Panon</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>Magasinier / Gestion des stocks</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>A vérifier</t>
+        </is>
+      </c>
+      <c r="S7" s="13" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>Activité exacte à confirmer via le code APE. Si location de matériel : il y a un parc et un magasin à gérer, donc un vrai poste d'apprenti.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U6"/>
+  <autoFilter ref="A4:V7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6303,7 +8183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6315,18 +8195,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6391,60 +8272,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6501,51 +8387,56 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>https://www.groupe-camalon.com/</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Opérateur logistique / Prépa. commandes</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>Créée en 1990. Denrées alimentaires, agrégats, ADR. Site : groupe-camalon.com — structure solide, très bon potentiel tuteur.</t>
         </is>
@@ -6602,51 +8493,56 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="N6" s="19" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
         <is>
           <t>https://www.transcoopoi.re/</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Agent de quai / Réception-expédition</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr">
         <is>
           <t>Site : transcoopoi.re</t>
         </is>
@@ -6703,15 +8599,15 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -6721,33 +8617,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Magasinier / Gestion des stocks</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>Employeur public : apprentissage possible dans la fonction publique hospitalière. Magasin général, pharmacie, flux de médicaments et équipements.</t>
         </is>
@@ -6804,15 +8705,15 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -6822,33 +8723,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R8" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S8" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T8" s="20" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="17" t="inlineStr">
         <is>
           <t>Hyper : réception, réserve, drive. Passer par le directeur de magasin + RH régionale.</t>
         </is>
@@ -6905,15 +8811,15 @@
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -6923,63 +8829,175 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>Source annuaire</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="T9" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T9" s="14" t="inlineStr"/>
-      <c r="U9" s="11" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>Franchise indépendante : décision rapide, parler directement au dirigeant.</t>
         </is>
       </c>
     </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>TRANSPORT ROUTIER LEGROS</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Transport routier de fret interurbain</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>800 chemin Commence</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>97437</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Sainte-Anne (Saint-Benoît)</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>A VERIFIER</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>Dirigeant / DG</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t>Opérateur logistique / Prépa. commandes</t>
+        </is>
+      </c>
+      <c r="Q10" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="R10" s="15" t="inlineStr">
+        <is>
+          <t>Source annuaire</t>
+        </is>
+      </c>
+      <c r="S10" s="19" t="inlineStr">
+        <is>
+          <t>Ouvrir la fiche entreprise</t>
+        </is>
+      </c>
+      <c r="T10" s="15" t="inlineStr">
+        <is>
+          <t>A contacter</t>
+        </is>
+      </c>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="17" t="inlineStr">
+        <is>
+          <t>SARL créée en 2021, transports routiers de fret interurbains. Structure jeune : argument « formez dès maintenant votre futur exploitant / préparateur ».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:U9"/>
+  <autoFilter ref="A4:V10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6991,7 +9009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7003,18 +9021,19 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -7079,60 +9098,65 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>Effectif (tranche INSEE)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Dirigeant (Nom Prénom)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Fonction</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Téléphone</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Email contact</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Site web</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Poste apprenti visé</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Fiabilité donnée</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Vérifier SIRET / APE / Dirigeant</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Statut prospection</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Date dernier contact</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7189,15 +9213,15 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -7207,33 +9231,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>A vérifier</t>
         </is>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr"/>
+      <c r="V5" s="11" t="inlineStr">
         <is>
           <t>Aucune entreprise logistique pure identifiée en source ouverte. Cibler : supérettes, négoces de matériaux, transporteurs indépendants. Méthode : mairie + agence Pôle emploi / France Travail de Saint-Benoît.</t>
         </is>
@@ -7290,15 +9319,15 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -7308,33 +9337,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>A vérifier</t>
         </is>
       </c>
-      <c r="R6" s="19" t="inlineStr">
+      <c r="S6" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S6" s="15" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="17" t="inlineStr">
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="17" t="inlineStr">
         <is>
           <t>Commerces de proximité, artisans, transport de matériaux. Faible densité logistique.</t>
         </is>
@@ -7391,15 +9425,15 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -7409,33 +9443,38 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>A vérifier</t>
         </is>
       </c>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>Hauteurs : agriculture (chouchou), transport de denrées, coopératives. Contacter la Chambre d'agriculture et les coopératives locales.</t>
         </is>
@@ -7492,15 +9531,15 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
           <t>Dirigeant / DG</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
-        <is>
-          <t>A COMPLETER</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>A COMPLETER</t>
         </is>
@@ -7510,60 +9549,65 @@
           <t>A COMPLETER</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>A COMPLETER</t>
+        </is>
+      </c>
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>Employé logistique en magasin</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>A vérifier</t>
         </is>
       </c>
-      <c r="R8" s="19" t="inlineStr">
+      <c r="S8" s="19" t="inlineStr">
         <is>
           <t>Ouvrir la fiche entreprise</t>
         </is>
       </c>
-      <c r="S8" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>A contacter</t>
         </is>
       </c>
-      <c r="T8" s="20" t="inlineStr"/>
-      <c r="U8" s="17" t="inlineStr">
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="17" t="inlineStr">
         <is>
           <t>Peu de logistique en hauteur : viser les dépôts et commerces de proximité, et les entreprises du bas où les jeunes des hauteurs peuvent se rendre.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U8"/>
+  <autoFilter ref="A4:V8"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="S5:S404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T5:T404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A contacter,Message laissé,RDV pris,Visite faite,Offre déposée,Candidat proposé,Contrat signé,Sans suite"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q5:Q404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Vérifié,Source annuaire,A vérifier"</formula1>
+    <dataValidation sqref="R5:R404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Vérifié INSEE,Vérifié,Source annuaire,A vérifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7646,18 +9690,18 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" s="23">
-        <f>COUNTIF('01 Saint-Denis'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('01 Saint-Denis'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D6" s="23">
-        <f>COUNTIF('01 Saint-Denis'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('01 Saint-Denis'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E6" s="23">
-        <f>COUNTIF('01 Saint-Denis'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('01 Saint-Denis'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F6" s="24">
@@ -7672,18 +9716,18 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('02 Sainte-Marie'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('02 Sainte-Marie'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>COUNTIF('02 Sainte-Marie'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('02 Sainte-Marie'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E7" s="23">
-        <f>COUNTIF('02 Sainte-Marie'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('02 Sainte-Marie'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F7" s="24">
@@ -7701,15 +9745,15 @@
         <v>4</v>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('03 Sainte-Suzanne'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('03 Sainte-Suzanne'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>COUNTIF('03 Sainte-Suzanne'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('03 Sainte-Suzanne'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E8" s="23">
-        <f>COUNTIF('03 Sainte-Suzanne'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('03 Sainte-Suzanne'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F8" s="24">
@@ -7724,18 +9768,18 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('04 Saint-André'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('04 Saint-André'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>COUNTIF('04 Saint-André'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('04 Saint-André'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E9" s="23">
-        <f>COUNTIF('04 Saint-André'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('04 Saint-André'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F9" s="24">
@@ -7750,18 +9794,18 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('05 Bras-Panon'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('05 Bras-Panon'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>COUNTIF('05 Bras-Panon'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('05 Bras-Panon'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E10" s="23">
-        <f>COUNTIF('05 Bras-Panon'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('05 Bras-Panon'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F10" s="24">
@@ -7776,18 +9820,18 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('06 Saint-Benoît'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('06 Saint-Benoît'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>COUNTIF('06 Saint-Benoît'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('06 Saint-Benoît'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E11" s="23">
-        <f>COUNTIF('06 Saint-Benoît'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('06 Saint-Benoît'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F11" s="24">
@@ -7805,15 +9849,15 @@
         <v>4</v>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('07 Sainte-Rose &amp; Hauteurs'!$S$5:$S$400,"A contacter")</f>
+        <f>COUNTIF('07 Sainte-Rose &amp; Hauteurs'!$T$5:$T$400,"A contacter")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>COUNTIF('07 Sainte-Rose &amp; Hauteurs'!$S$5:$S$400,"RDV pris")</f>
+        <f>COUNTIF('07 Sainte-Rose &amp; Hauteurs'!$T$5:$T$400,"RDV pris")</f>
         <v/>
       </c>
       <c r="E12" s="23">
-        <f>COUNTIF('07 Sainte-Rose &amp; Hauteurs'!$S$5:$S$400,"Contrat signé")</f>
+        <f>COUNTIF('07 Sainte-Rose &amp; Hauteurs'!$T$5:$T$400,"Contrat signé")</f>
         <v/>
       </c>
       <c r="F12" s="24">
